--- a/data/WP17/WP17_auswertung_abgeordnete.xlsx
+++ b/data/WP17/WP17_auswertung_abgeordnete.xlsx
@@ -725,13 +725,13 @@
         <v>381</v>
       </c>
       <c r="D2" t="n">
-        <v>32.2928759894459</v>
+        <v>32.3070866141732</v>
       </c>
       <c r="E2" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F2" t="n">
-        <v>30.4461942257218</v>
+        <v>29.9212598425197</v>
       </c>
     </row>
     <row r="3">
@@ -742,16 +742,16 @@
         <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D3" t="n">
-        <v>27.115625</v>
+        <v>27.0990712074303</v>
       </c>
       <c r="E3" t="n">
         <v>119</v>
       </c>
       <c r="F3" t="n">
-        <v>63.0434782608696</v>
+        <v>63.1578947368421</v>
       </c>
     </row>
     <row r="4">
@@ -785,7 +785,7 @@
         <v>300</v>
       </c>
       <c r="D5" t="n">
-        <v>30.7056856187291</v>
+        <v>30.6033333333333</v>
       </c>
       <c r="E5" t="n">
         <v>183</v>
@@ -905,7 +905,7 @@
         <v>223</v>
       </c>
       <c r="D11" t="n">
-        <v>29.8873873873874</v>
+        <v>29.8565022421525</v>
       </c>
       <c r="E11" t="n">
         <v>117</v>
@@ -922,16 +922,16 @@
         <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D12" t="n">
-        <v>31.8177339901478</v>
+        <v>31.7463414634146</v>
       </c>
       <c r="E12" t="n">
         <v>132</v>
       </c>
       <c r="F12" t="n">
-        <v>35.2941176470588</v>
+        <v>35.609756097561</v>
       </c>
     </row>
     <row r="13">
@@ -1065,7 +1065,7 @@
         <v>162</v>
       </c>
       <c r="D19" t="n">
-        <v>28.6024844720497</v>
+        <v>28.4259259259259</v>
       </c>
       <c r="E19" t="n">
         <v>93</v>
@@ -1185,13 +1185,13 @@
         <v>130</v>
       </c>
       <c r="D25" t="n">
-        <v>30.6356589147287</v>
+        <v>30.6769230769231</v>
       </c>
       <c r="E25" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F25" t="n">
-        <v>48.4615384615385</v>
+        <v>47.6923076923077</v>
       </c>
     </row>
     <row r="26">
@@ -1265,13 +1265,13 @@
         <v>121</v>
       </c>
       <c r="D29" t="n">
-        <v>31.0666666666667</v>
+        <v>31.1074380165289</v>
       </c>
       <c r="E29" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F29" t="n">
-        <v>42.9752066115703</v>
+        <v>42.1487603305785</v>
       </c>
     </row>
     <row r="30">
@@ -1382,16 +1382,16 @@
         <v>7</v>
       </c>
       <c r="C35" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D35" t="n">
-        <v>33.5454545454545</v>
+        <v>33.4719101123596</v>
       </c>
       <c r="E35" t="n">
         <v>63</v>
       </c>
       <c r="F35" t="n">
-        <v>28.4090909090909</v>
+        <v>29.2134831460674</v>
       </c>
     </row>
     <row r="36">
@@ -1605,7 +1605,7 @@
         <v>66</v>
       </c>
       <c r="D46" t="n">
-        <v>29.5384615384615</v>
+        <v>29.3787878787879</v>
       </c>
       <c r="E46" t="n">
         <v>32</v>
@@ -3088,13 +3088,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2992214F-8CD1-4E88-9ED0-ACA78C9EC02D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33AFFC4F-ADA1-4E7F-B763-523A60733EDA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AE0548C-4587-40E4-88A2-B179B77A2DCC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FE93001-7028-4B1A-B426-EED258F4B7DF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8FE2E64-E513-413E-8185-9B3BDF056E73}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D70109CF-5EF4-4461-AB29-A75A2E10B8A1}"/>
 </file>
--- a/data/WP17/WP17_auswertung_abgeordnete.xlsx
+++ b/data/WP17/WP17_auswertung_abgeordnete.xlsx
@@ -53,15 +53,18 @@
     <t xml:space="preserve">Wagner, Markus</t>
   </si>
   <si>
+    <t xml:space="preserve">Dr. Vincentz, Martin</t>
+  </si>
+  <si>
     <t xml:space="preserve">Brems, Wibke</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr. Vincentz, Martin</t>
-  </si>
-  <si>
     <t xml:space="preserve">Walger-Demolsky, Gabriele</t>
   </si>
   <si>
+    <t xml:space="preserve">Becker, Horst</t>
+  </si>
+  <si>
     <t xml:space="preserve">Keith, Andreas</t>
   </si>
   <si>
@@ -74,22 +77,25 @@
     <t xml:space="preserve">AfD/fraktionslos</t>
   </si>
   <si>
-    <t xml:space="preserve">Becker, Horst</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bolte-Richter, Matthi</t>
   </si>
   <si>
     <t xml:space="preserve">Klocke, Arndt</t>
   </si>
   <si>
+    <t xml:space="preserve">Voigt-Küppers, Eva-Maria</t>
+  </si>
+  <si>
     <t xml:space="preserve">Loose, Christian</t>
   </si>
   <si>
+    <t xml:space="preserve">Röckemann, Thomas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dr. Maelzer, Dennis</t>
   </si>
   <si>
-    <t xml:space="preserve">Voigt-Küppers, Eva-Maria</t>
+    <t xml:space="preserve">Schäffer, Verena</t>
   </si>
   <si>
     <t xml:space="preserve">Beer, Sigrid</t>
@@ -98,15 +104,15 @@
     <t xml:space="preserve">Vogel, Nic Peter</t>
   </si>
   <si>
-    <t xml:space="preserve">Röckemann, Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schäffer, Verena</t>
-  </si>
-  <si>
     <t xml:space="preserve">Remmel, Johannes</t>
   </si>
   <si>
+    <t xml:space="preserve">Pretzell, Marcus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mostofizadeh, Mehrdad</t>
+  </si>
+  <si>
     <t xml:space="preserve">Strotebeck, Herbert</t>
   </si>
   <si>
@@ -122,145 +128,154 @@
     <t xml:space="preserve">Berg, Guido van den</t>
   </si>
   <si>
+    <t xml:space="preserve">Dr. Blex, Christian</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dudas, Gordan</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr. Blex, Christian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mostofizadeh, Mehrdad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wolf, Sven</t>
   </si>
   <si>
+    <t xml:space="preserve">Sundermann, Frank</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kutschaty, Thomas</t>
   </si>
   <si>
     <t xml:space="preserve">Butschkau, Anja</t>
   </si>
   <si>
-    <t xml:space="preserve">Pretzell, Marcus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sundermann, Frank</t>
-  </si>
-  <si>
     <t xml:space="preserve">Schneider, René</t>
   </si>
   <si>
     <t xml:space="preserve">SPD/GRÜNE</t>
   </si>
   <si>
+    <t xml:space="preserve">Dworeck-Danielowski, Iris</t>
+  </si>
+  <si>
     <t xml:space="preserve">Schultheis, Karl</t>
   </si>
   <si>
+    <t xml:space="preserve">Paul, Josefine</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yetim, Ibrahim</t>
   </si>
   <si>
-    <t xml:space="preserve">Dworeck-Danielowski, Iris</t>
+    <t xml:space="preserve">Berghahn, Jürgen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zimkeit, Stefan</t>
   </si>
   <si>
     <t xml:space="preserve">Löcker, Carsten</t>
   </si>
   <si>
+    <t xml:space="preserve">Vogt, Alexander</t>
+  </si>
+  <si>
     <t xml:space="preserve">dos Santos Herrmann, Susana</t>
   </si>
   <si>
-    <t xml:space="preserve">Zimkeit, Stefan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paul, Josefine</t>
-  </si>
-  <si>
     <t xml:space="preserve">Börschel, Martin</t>
   </si>
   <si>
-    <t xml:space="preserve">Vogt, Alexander</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berghahn, Jürgen</t>
+    <t xml:space="preserve">Kampmann, Christina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lück, Angela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neumann, Josef</t>
   </si>
   <si>
     <t xml:space="preserve">Müller-Witt, Elisabeth</t>
   </si>
   <si>
-    <t xml:space="preserve">Kampmann, Christina</t>
+    <t xml:space="preserve">Aymaz, Berivan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engstfeld, Stefan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kapteinat, Lisa-Kristin</t>
   </si>
   <si>
     <t xml:space="preserve">Weiß, Rüdiger</t>
   </si>
   <si>
-    <t xml:space="preserve">Aymaz, Berivan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kapteinat, Lisa-Kristin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lück, Angela</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hübner, Michael R.</t>
   </si>
   <si>
-    <t xml:space="preserve">Engstfeld, Stefan</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lux, Eva</t>
   </si>
   <si>
     <t xml:space="preserve">Watermeier, Sebastian</t>
   </si>
   <si>
+    <t xml:space="preserve">Müller, Frank</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dahm, Christian</t>
   </si>
   <si>
+    <t xml:space="preserve">Bell, Dietmar</t>
+  </si>
+  <si>
     <t xml:space="preserve">Blask, Inge</t>
   </si>
   <si>
-    <t xml:space="preserve">Bell, Dietmar</t>
-  </si>
-  <si>
     <t xml:space="preserve">Düker, Monika</t>
   </si>
   <si>
-    <t xml:space="preserve">Neumann, Josef</t>
+    <t xml:space="preserve">Lüders, Nadja</t>
   </si>
   <si>
     <t xml:space="preserve">Altenkamp, Britta</t>
   </si>
   <si>
-    <t xml:space="preserve">Müller, Frank</t>
-  </si>
-  <si>
     <t xml:space="preserve">Beckamp, Roger</t>
   </si>
   <si>
+    <t xml:space="preserve">Börner, Frank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kossiski, Andreas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stinka, André</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stock, Ellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weng, Christina</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jörg, Wolfgang</t>
   </si>
   <si>
-    <t xml:space="preserve">Stinka, André</t>
+    <t xml:space="preserve">Kopp-Herr, Regina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bischoff, Rainer</t>
   </si>
   <si>
     <t xml:space="preserve">Becker, Andreas</t>
   </si>
   <si>
+    <t xml:space="preserve">Ganzke, Hartmut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gebhard, Heike</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bialas, Andreas</t>
   </si>
   <si>
-    <t xml:space="preserve">Börner, Frank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ganzke, Hartmut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gebhard, Heike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kossiski, Andreas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weng, Christina</t>
+    <t xml:space="preserve">Yüksel, Serdar</t>
   </si>
   <si>
     <t xml:space="preserve">Bongers, Sonja</t>
@@ -269,70 +284,61 @@
     <t xml:space="preserve">Weske, Markus Herbert</t>
   </si>
   <si>
-    <t xml:space="preserve">Kopp-Herr, Regina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lüders, Nadja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stock, Ellen</t>
-  </si>
-  <si>
     <t xml:space="preserve">Spanier-Oppermann, Ina</t>
   </si>
   <si>
-    <t xml:space="preserve">Bischoff, Rainer</t>
+    <t xml:space="preserve">Fortmeier, Georg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rahe, Ernst-Wilhelm</t>
   </si>
   <si>
     <t xml:space="preserve">Körfges, Hans-Willi</t>
   </si>
   <si>
-    <t xml:space="preserve">Yüksel, Serdar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rahe, Ernst-Wilhelm</t>
+    <t xml:space="preserve">Watermann-Krass, Annette</t>
   </si>
   <si>
     <t xml:space="preserve">Stotz, Marlies</t>
   </si>
   <si>
+    <t xml:space="preserve">Hammelrath, Gabriele</t>
+  </si>
+  <si>
     <t xml:space="preserve">Baran, Volkan</t>
   </si>
   <si>
-    <t xml:space="preserve">Watermann-Krass, Annette</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fortmeier, Georg</t>
+    <t xml:space="preserve">Jäger, Ralf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prof. Dr. Rudolph, Karsten</t>
   </si>
   <si>
     <t xml:space="preserve">Dr. Büteführ, Nadja</t>
   </si>
   <si>
+    <t xml:space="preserve">Keymis, Oliver</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gödecke, Carina</t>
   </si>
   <si>
-    <t xml:space="preserve">Hammelrath, Gabriele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prof. Dr. Rudolph, Karsten</t>
+    <t xml:space="preserve">Jahl, Armin</t>
   </si>
   <si>
     <t xml:space="preserve">Steffens, Barbara</t>
   </si>
   <si>
+    <t xml:space="preserve">Göddertz, Thomas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Herter, Marc</t>
   </si>
   <si>
     <t xml:space="preserve">Kraft, Hannelore</t>
   </si>
   <si>
-    <t xml:space="preserve">Göddertz, Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jäger, Ralf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keymis, Oliver</t>
+    <t xml:space="preserve">Kramer, Hubertus</t>
   </si>
   <si>
     <t xml:space="preserve">Prof. Dr. Bovermann, Rainer</t>
@@ -344,16 +350,10 @@
     <t xml:space="preserve">Cordes, Frederick</t>
   </si>
   <si>
+    <t xml:space="preserve">Römer, Norbert</t>
+  </si>
+  <si>
     <t xml:space="preserve">Andrieshen, Nina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kramer, Hubertus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Römer, Norbert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jahl, Armin</t>
   </si>
   <si>
     <t xml:space="preserve">Schulze, Svenja</t>
@@ -722,16 +722,16 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="D2" t="n">
-        <v>32.3070866141732</v>
+        <v>32.2196382428941</v>
       </c>
       <c r="E2" t="n">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F2" t="n">
-        <v>29.9212598425197</v>
+        <v>29.7157622739018</v>
       </c>
     </row>
     <row r="3">
@@ -742,16 +742,16 @@
         <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>27.0990712074303</v>
+        <v>26.4474474474474</v>
       </c>
       <c r="E3" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F3" t="n">
-        <v>63.1578947368421</v>
+        <v>64.5645645645646</v>
       </c>
     </row>
     <row r="4">
@@ -762,16 +762,16 @@
         <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="D4" t="n">
-        <v>30.8046357615894</v>
+        <v>30.6785714285714</v>
       </c>
       <c r="E4" t="n">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="F4" t="n">
-        <v>39.0728476821192</v>
+        <v>50.6493506493507</v>
       </c>
     </row>
     <row r="5">
@@ -782,16 +782,16 @@
         <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D5" t="n">
-        <v>30.6033333333333</v>
+        <v>31.1023102310231</v>
       </c>
       <c r="E5" t="n">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>41.2541254125413</v>
       </c>
     </row>
     <row r="6">
@@ -799,19 +799,19 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D6" t="n">
-        <v>35.2727272727273</v>
+        <v>35.8529411764706</v>
       </c>
       <c r="E6" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>24.6323529411765</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +819,19 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D7" t="n">
-        <v>35.8022813688213</v>
+        <v>34.6642066420664</v>
       </c>
       <c r="E7" t="n">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="F7" t="n">
-        <v>26.2357414448669</v>
+        <v>25.0922509225092</v>
       </c>
     </row>
     <row r="8">
@@ -842,16 +842,16 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="D8" t="n">
-        <v>31.5801526717557</v>
+        <v>32.0373134328358</v>
       </c>
       <c r="E8" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F8" t="n">
-        <v>33.587786259542</v>
+        <v>34.7014925373134</v>
       </c>
     </row>
     <row r="9">
@@ -859,19 +859,19 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="D9" t="n">
-        <v>31.4502164502164</v>
+        <v>31.6260162601626</v>
       </c>
       <c r="E9" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="F9" t="n">
-        <v>33.7662337662338</v>
+        <v>34.5528455284553</v>
       </c>
     </row>
     <row r="10">
@@ -879,19 +879,19 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>31.6228070175439</v>
+        <v>31.6311475409836</v>
       </c>
       <c r="E10" t="n">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="F10" t="n">
-        <v>42.9824561403509</v>
+        <v>33.6065573770492</v>
       </c>
     </row>
     <row r="11">
@@ -899,39 +899,39 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="D11" t="n">
-        <v>29.8565022421525</v>
+        <v>31.8559670781893</v>
       </c>
       <c r="E11" t="n">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="F11" t="n">
-        <v>47.5336322869955</v>
+        <v>41.5637860082305</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
         <v>20</v>
       </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
       <c r="C12" t="n">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="D12" t="n">
-        <v>31.7463414634146</v>
+        <v>29.7982062780269</v>
       </c>
       <c r="E12" t="n">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="F12" t="n">
-        <v>35.609756097561</v>
+        <v>46.6367713004484</v>
       </c>
     </row>
     <row r="13">
@@ -942,16 +942,16 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="D13" t="n">
-        <v>33.7980295566502</v>
+        <v>32.8603603603604</v>
       </c>
       <c r="E13" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F13" t="n">
-        <v>27.5862068965517</v>
+        <v>32.4324324324324</v>
       </c>
     </row>
     <row r="14">
@@ -962,16 +962,16 @@
         <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="D14" t="n">
-        <v>32.3947368421053</v>
+        <v>31.7647058823529</v>
       </c>
       <c r="E14" t="n">
         <v>132</v>
       </c>
       <c r="F14" t="n">
-        <v>30.5263157894737</v>
+        <v>35.2941176470588</v>
       </c>
     </row>
     <row r="15">
@@ -979,19 +979,19 @@
         <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D15" t="n">
-        <v>31.0751445086705</v>
+        <v>31.6032608695652</v>
       </c>
       <c r="E15" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F15" t="n">
-        <v>34.6820809248555</v>
+        <v>39.6739130434783</v>
       </c>
     </row>
     <row r="16">
@@ -999,19 +999,19 @@
         <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="D16" t="n">
-        <v>31.6424242424242</v>
+        <v>31.3005464480874</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="F16" t="n">
-        <v>39.3939393939394</v>
+        <v>36.6120218579235</v>
       </c>
     </row>
     <row r="17">
@@ -1019,19 +1019,19 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D17" t="n">
-        <v>31.5636363636364</v>
+        <v>32.1396648044693</v>
       </c>
       <c r="E17" t="n">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="F17" t="n">
-        <v>40</v>
+        <v>31.8435754189944</v>
       </c>
     </row>
     <row r="18">
@@ -1039,19 +1039,19 @@
         <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="D18" t="n">
-        <v>32.7361963190184</v>
+        <v>31.8</v>
       </c>
       <c r="E18" t="n">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="F18" t="n">
-        <v>39.2638036809816</v>
+        <v>33.7142857142857</v>
       </c>
     </row>
     <row r="19">
@@ -1059,19 +1059,19 @@
         <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="D19" t="n">
-        <v>28.4259259259259</v>
+        <v>30.112426035503</v>
       </c>
       <c r="E19" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F19" t="n">
-        <v>42.5925925925926</v>
+        <v>42.0118343195266</v>
       </c>
     </row>
     <row r="20">
@@ -1079,19 +1079,19 @@
         <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D20" t="n">
-        <v>30.9130434782609</v>
+        <v>32.0952380952381</v>
       </c>
       <c r="E20" t="n">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="F20" t="n">
-        <v>34.7826086956522</v>
+        <v>41.6666666666667</v>
       </c>
     </row>
     <row r="21">
@@ -1099,19 +1099,19 @@
         <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C21" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="D21" t="n">
-        <v>30.89375</v>
+        <v>29.6964285714286</v>
       </c>
       <c r="E21" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>35.625</v>
+        <v>40.4761904761905</v>
       </c>
     </row>
     <row r="22">
@@ -1122,16 +1122,16 @@
         <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="D22" t="n">
-        <v>35.2291666666667</v>
+        <v>34.2994011976048</v>
       </c>
       <c r="E22" t="n">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="F22" t="n">
-        <v>16.6666666666667</v>
+        <v>19.7604790419162</v>
       </c>
     </row>
     <row r="23">
@@ -1139,19 +1139,19 @@
         <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C23" t="n">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="D23" t="n">
-        <v>33.75</v>
+        <v>29.8791946308725</v>
       </c>
       <c r="E23" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F23" t="n">
-        <v>35.6060606060606</v>
+        <v>44.9664429530201</v>
       </c>
     </row>
     <row r="24">
@@ -1159,19 +1159,19 @@
         <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C24" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D24" t="n">
-        <v>29.6412213740458</v>
+        <v>31.9208633093525</v>
       </c>
       <c r="E24" t="n">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F24" t="n">
-        <v>45.8015267175573</v>
+        <v>31.6546762589928</v>
       </c>
     </row>
     <row r="25">
@@ -1182,16 +1182,16 @@
         <v>11</v>
       </c>
       <c r="C25" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="D25" t="n">
-        <v>30.6769230769231</v>
+        <v>33.6423357664234</v>
       </c>
       <c r="E25" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F25" t="n">
-        <v>47.6923076923077</v>
+        <v>34.3065693430657</v>
       </c>
     </row>
     <row r="26">
@@ -1199,19 +1199,19 @@
         <v>34</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D26" t="n">
-        <v>31.062015503876</v>
+        <v>29.2835820895522</v>
       </c>
       <c r="E26" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F26" t="n">
-        <v>34.8837209302326</v>
+        <v>41.044776119403</v>
       </c>
     </row>
     <row r="27">
@@ -1219,19 +1219,19 @@
         <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C27" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D27" t="n">
-        <v>34.2539682539683</v>
+        <v>31.1119402985075</v>
       </c>
       <c r="E27" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F27" t="n">
-        <v>26.984126984127</v>
+        <v>44.0298507462687</v>
       </c>
     </row>
     <row r="28">
@@ -1239,19 +1239,19 @@
         <v>36</v>
       </c>
       <c r="B28" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C28" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="D28" t="n">
-        <v>28.1967213114754</v>
+        <v>31.5572519083969</v>
       </c>
       <c r="E28" t="n">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="F28" t="n">
-        <v>47.5409836065574</v>
+        <v>32.824427480916</v>
       </c>
     </row>
     <row r="29">
@@ -1259,19 +1259,19 @@
         <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C29" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D29" t="n">
-        <v>31.1074380165289</v>
+        <v>33.244094488189</v>
       </c>
       <c r="E29" t="n">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="F29" t="n">
-        <v>42.1487603305785</v>
+        <v>27.5590551181102</v>
       </c>
     </row>
     <row r="30">
@@ -1279,19 +1279,19 @@
         <v>38</v>
       </c>
       <c r="B30" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C30" t="n">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="D30" t="n">
-        <v>32.0384615384615</v>
+        <v>32.1338582677165</v>
       </c>
       <c r="E30" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F30" t="n">
-        <v>33.6538461538462</v>
+        <v>40.9448818897638</v>
       </c>
     </row>
     <row r="31">
@@ -1302,16 +1302,16 @@
         <v>7</v>
       </c>
       <c r="C31" t="n">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="D31" t="n">
-        <v>29.3137254901961</v>
+        <v>27.9274193548387</v>
       </c>
       <c r="E31" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="F31" t="n">
-        <v>51.9607843137255</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32">
@@ -1322,16 +1322,16 @@
         <v>7</v>
       </c>
       <c r="C32" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="D32" t="n">
-        <v>45.6236559139785</v>
+        <v>29.447619047619</v>
       </c>
       <c r="E32" t="n">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="F32" t="n">
-        <v>5.3763440860215</v>
+        <v>46.6666666666667</v>
       </c>
     </row>
     <row r="33">
@@ -1342,16 +1342,16 @@
         <v>7</v>
       </c>
       <c r="C33" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D33" t="n">
-        <v>32.2696629213483</v>
+        <v>35.02</v>
       </c>
       <c r="E33" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="F33" t="n">
-        <v>30.3370786516854</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
@@ -1359,19 +1359,19 @@
         <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C34" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D34" t="n">
-        <v>28.6179775280899</v>
+        <v>47.4285714285714</v>
       </c>
       <c r="E34" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F34" t="n">
-        <v>57.3033707865169</v>
+        <v>8.16326530612244</v>
       </c>
     </row>
     <row r="35">
@@ -1382,16 +1382,16 @@
         <v>7</v>
       </c>
       <c r="C35" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D35" t="n">
-        <v>33.4719101123596</v>
+        <v>31.8</v>
       </c>
       <c r="E35" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F35" t="n">
-        <v>29.2134831460674</v>
+        <v>31.1111111111111</v>
       </c>
     </row>
     <row r="36">
@@ -1402,16 +1402,16 @@
         <v>45</v>
       </c>
       <c r="C36" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D36" t="n">
-        <v>29.1379310344828</v>
+        <v>28.5056179775281</v>
       </c>
       <c r="E36" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F36" t="n">
-        <v>48.2758620689655</v>
+        <v>52.808988764045</v>
       </c>
     </row>
     <row r="37">
@@ -1419,19 +1419,19 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C37" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D37" t="n">
-        <v>30.620253164557</v>
+        <v>34.1264367816092</v>
       </c>
       <c r="E37" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="F37" t="n">
-        <v>46.8354430379747</v>
+        <v>34.4827586206897</v>
       </c>
     </row>
     <row r="38">
@@ -1442,16 +1442,16 @@
         <v>7</v>
       </c>
       <c r="C38" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D38" t="n">
-        <v>30.7435897435897</v>
+        <v>30.9767441860465</v>
       </c>
       <c r="E38" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F38" t="n">
-        <v>44.8717948717949</v>
+        <v>43.0232558139535</v>
       </c>
     </row>
     <row r="39">
@@ -1459,19 +1459,19 @@
         <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C39" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D39" t="n">
-        <v>31.4473684210526</v>
+        <v>30.2530120481928</v>
       </c>
       <c r="E39" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F39" t="n">
-        <v>42.1052631578947</v>
+        <v>40.9638554216867</v>
       </c>
     </row>
     <row r="40">
@@ -1482,16 +1482,16 @@
         <v>7</v>
       </c>
       <c r="C40" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D40" t="n">
-        <v>31.0958904109589</v>
+        <v>30.6144578313253</v>
       </c>
       <c r="E40" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F40" t="n">
-        <v>45.2054794520548</v>
+        <v>40.9638554216867</v>
       </c>
     </row>
     <row r="41">
@@ -1502,16 +1502,16 @@
         <v>7</v>
       </c>
       <c r="C41" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D41" t="n">
-        <v>29.5616438356164</v>
+        <v>31.2125</v>
       </c>
       <c r="E41" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="F41" t="n">
-        <v>54.7945205479452</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="42">
@@ -1522,16 +1522,16 @@
         <v>7</v>
       </c>
       <c r="C42" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D42" t="n">
-        <v>28</v>
+        <v>29.325</v>
       </c>
       <c r="E42" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F42" t="n">
-        <v>50</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="43">
@@ -1539,19 +1539,19 @@
         <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C43" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D43" t="n">
-        <v>30.0140845070423</v>
+        <v>31.4025974025974</v>
       </c>
       <c r="E43" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F43" t="n">
-        <v>45.0704225352113</v>
+        <v>41.5584415584416</v>
       </c>
     </row>
     <row r="44">
@@ -1562,16 +1562,16 @@
         <v>7</v>
       </c>
       <c r="C44" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D44" t="n">
-        <v>30.8358208955224</v>
+        <v>29.6756756756757</v>
       </c>
       <c r="E44" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F44" t="n">
-        <v>35.8208955223881</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45">
@@ -1582,16 +1582,16 @@
         <v>7</v>
       </c>
       <c r="C45" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D45" t="n">
-        <v>29.8507462686567</v>
+        <v>29.6891891891892</v>
       </c>
       <c r="E45" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F45" t="n">
-        <v>47.7611940298507</v>
+        <v>54.054054054054</v>
       </c>
     </row>
     <row r="46">
@@ -1602,16 +1602,16 @@
         <v>7</v>
       </c>
       <c r="C46" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D46" t="n">
-        <v>29.3787878787879</v>
+        <v>30.7571428571429</v>
       </c>
       <c r="E46" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="F46" t="n">
-        <v>51.5151515151515</v>
+        <v>35.7142857142857</v>
       </c>
     </row>
     <row r="47">
@@ -1622,16 +1622,16 @@
         <v>7</v>
       </c>
       <c r="C47" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D47" t="n">
-        <v>31.2295081967213</v>
+        <v>38.3636363636364</v>
       </c>
       <c r="E47" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F47" t="n">
-        <v>24.5901639344262</v>
+        <v>16.6666666666667</v>
       </c>
     </row>
     <row r="48">
@@ -1642,16 +1642,16 @@
         <v>7</v>
       </c>
       <c r="C48" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D48" t="n">
-        <v>37.8474576271186</v>
+        <v>30.1384615384615</v>
       </c>
       <c r="E48" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F48" t="n">
-        <v>16.9491525423729</v>
+        <v>41.5384615384615</v>
       </c>
     </row>
     <row r="49">
@@ -1662,16 +1662,16 @@
         <v>7</v>
       </c>
       <c r="C49" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D49" t="n">
-        <v>30.5862068965517</v>
+        <v>31.2063492063492</v>
       </c>
       <c r="E49" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F49" t="n">
-        <v>41.3793103448276</v>
+        <v>47.6190476190476</v>
       </c>
     </row>
     <row r="50">
@@ -1679,19 +1679,19 @@
         <v>59</v>
       </c>
       <c r="B50" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C50" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D50" t="n">
-        <v>32.7142857142857</v>
+        <v>30.3548387096774</v>
       </c>
       <c r="E50" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F50" t="n">
-        <v>33.9285714285714</v>
+        <v>45.1612903225806</v>
       </c>
     </row>
     <row r="51">
@@ -1699,19 +1699,19 @@
         <v>60</v>
       </c>
       <c r="B51" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C51" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D51" t="n">
-        <v>30.6785714285714</v>
+        <v>31.5573770491803</v>
       </c>
       <c r="E51" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F51" t="n">
-        <v>39.2857142857143</v>
+        <v>39.344262295082</v>
       </c>
     </row>
     <row r="52">
@@ -1719,19 +1719,19 @@
         <v>61</v>
       </c>
       <c r="B52" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C52" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>28.3392857142857</v>
+        <v>29.4833333333333</v>
       </c>
       <c r="E52" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F52" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53">
@@ -1742,16 +1742,16 @@
         <v>7</v>
       </c>
       <c r="C53" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>31.3888888888889</v>
+        <v>30.6166666666667</v>
       </c>
       <c r="E53" t="n">
         <v>34</v>
       </c>
       <c r="F53" t="n">
-        <v>37.037037037037</v>
+        <v>43.3333333333333</v>
       </c>
     </row>
     <row r="54">
@@ -1759,19 +1759,19 @@
         <v>63</v>
       </c>
       <c r="B54" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C54" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>30.2307692307692</v>
+        <v>30.6333333333333</v>
       </c>
       <c r="E54" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F54" t="n">
-        <v>42.3076923076923</v>
+        <v>43.3333333333333</v>
       </c>
     </row>
     <row r="55">
@@ -1782,16 +1782,16 @@
         <v>7</v>
       </c>
       <c r="C55" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D55" t="n">
-        <v>28.5961538461538</v>
+        <v>31.9824561403509</v>
       </c>
       <c r="E55" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F55" t="n">
-        <v>65.3846153846154</v>
+        <v>40.3508771929825</v>
       </c>
     </row>
     <row r="56">
@@ -1802,16 +1802,16 @@
         <v>7</v>
       </c>
       <c r="C56" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D56" t="n">
-        <v>31.0408163265306</v>
+        <v>28.1428571428571</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F56" t="n">
-        <v>38.7755102040816</v>
+        <v>60.7142857142857</v>
       </c>
     </row>
     <row r="57">
@@ -1822,16 +1822,16 @@
         <v>7</v>
       </c>
       <c r="C57" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D57" t="n">
-        <v>29.2083333333333</v>
+        <v>30.3518518518519</v>
       </c>
       <c r="E57" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F57" t="n">
-        <v>37.5</v>
+        <v>42.5925925925926</v>
       </c>
     </row>
     <row r="58">
@@ -1842,16 +1842,16 @@
         <v>7</v>
       </c>
       <c r="C58" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D58" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="E58" t="n">
         <v>31</v>
       </c>
-      <c r="E58" t="n">
-        <v>36</v>
-      </c>
       <c r="F58" t="n">
-        <v>20</v>
+        <v>40.3846153846154</v>
       </c>
     </row>
     <row r="59">
@@ -1862,16 +1862,16 @@
         <v>7</v>
       </c>
       <c r="C59" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D59" t="n">
-        <v>31.3636363636364</v>
+        <v>30.3</v>
       </c>
       <c r="E59" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F59" t="n">
-        <v>45.4545454545455</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60">
@@ -1879,19 +1879,19 @@
         <v>69</v>
       </c>
       <c r="B60" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C60" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D60" t="n">
-        <v>32.1860465116279</v>
+        <v>31.6458333333333</v>
       </c>
       <c r="E60" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F60" t="n">
-        <v>25.5813953488372</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="61">
@@ -1902,16 +1902,16 @@
         <v>7</v>
       </c>
       <c r="C61" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D61" t="n">
-        <v>30.0232558139535</v>
+        <v>30.0425531914894</v>
       </c>
       <c r="E61" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F61" t="n">
-        <v>53.4883720930233</v>
+        <v>21.2765957446808</v>
       </c>
     </row>
     <row r="62">
@@ -1919,19 +1919,19 @@
         <v>71</v>
       </c>
       <c r="B62" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="C62" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D62" t="n">
-        <v>29.0714285714286</v>
+        <v>32.0212765957447</v>
       </c>
       <c r="E62" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F62" t="n">
-        <v>33.3333333333333</v>
+        <v>31.9148936170213</v>
       </c>
     </row>
     <row r="63">
@@ -1942,16 +1942,16 @@
         <v>7</v>
       </c>
       <c r="C63" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D63" t="n">
-        <v>31.5365853658537</v>
+        <v>29.1395348837209</v>
       </c>
       <c r="E63" t="n">
         <v>25</v>
       </c>
       <c r="F63" t="n">
-        <v>39.0243902439024</v>
+        <v>41.8604651162791</v>
       </c>
     </row>
     <row r="64">
@@ -1959,19 +1959,19 @@
         <v>73</v>
       </c>
       <c r="B64" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C64" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D64" t="n">
-        <v>32</v>
+        <v>28.5714285714286</v>
       </c>
       <c r="E64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
-        <v>45</v>
+        <v>45.2380952380952</v>
       </c>
     </row>
     <row r="65">
@@ -1979,19 +1979,19 @@
         <v>74</v>
       </c>
       <c r="B65" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C65" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D65" t="n">
-        <v>28.2051282051282</v>
+        <v>33.5714285714286</v>
       </c>
       <c r="E65" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F65" t="n">
-        <v>51.2820512820513</v>
+        <v>38.0952380952381</v>
       </c>
     </row>
     <row r="66">
@@ -2002,16 +2002,16 @@
         <v>7</v>
       </c>
       <c r="C66" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D66" t="n">
-        <v>34.051282051282</v>
+        <v>30.6190476190476</v>
       </c>
       <c r="E66" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F66" t="n">
-        <v>28.2051282051282</v>
+        <v>38.0952380952381</v>
       </c>
     </row>
     <row r="67">
@@ -2022,16 +2022,16 @@
         <v>7</v>
       </c>
       <c r="C67" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D67" t="n">
-        <v>34.1428571428571</v>
+        <v>30.2682926829268</v>
       </c>
       <c r="E67" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F67" t="n">
-        <v>37.1428571428571</v>
+        <v>43.9024390243902</v>
       </c>
     </row>
     <row r="68">
@@ -2042,16 +2042,16 @@
         <v>7</v>
       </c>
       <c r="C68" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D68" t="n">
-        <v>33.4117647058824</v>
+        <v>33.8048780487805</v>
       </c>
       <c r="E68" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F68" t="n">
-        <v>35.2941176470588</v>
+        <v>34.1463414634146</v>
       </c>
     </row>
     <row r="69">
@@ -2062,16 +2062,16 @@
         <v>7</v>
       </c>
       <c r="C69" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D69" t="n">
-        <v>31.1818181818182</v>
+        <v>31.9512195121951</v>
       </c>
       <c r="E69" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F69" t="n">
-        <v>36.3636363636364</v>
+        <v>21.9512195121951</v>
       </c>
     </row>
     <row r="70">
@@ -2082,16 +2082,16 @@
         <v>7</v>
       </c>
       <c r="C70" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D70" t="n">
-        <v>30.7272727272727</v>
+        <v>30.4634146341463</v>
       </c>
       <c r="E70" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F70" t="n">
-        <v>45.4545454545455</v>
+        <v>43.9024390243902</v>
       </c>
     </row>
     <row r="71">
@@ -2102,16 +2102,16 @@
         <v>7</v>
       </c>
       <c r="C71" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D71" t="n">
-        <v>29.9090909090909</v>
+        <v>28.5</v>
       </c>
       <c r="E71" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F71" t="n">
-        <v>51.5151515151515</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72">
@@ -2122,16 +2122,16 @@
         <v>7</v>
       </c>
       <c r="C72" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D72" t="n">
-        <v>30.7272727272727</v>
+        <v>32.6052631578947</v>
       </c>
       <c r="E72" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F72" t="n">
-        <v>39.3939393939394</v>
+        <v>23.6842105263158</v>
       </c>
     </row>
     <row r="73">
@@ -2142,16 +2142,16 @@
         <v>7</v>
       </c>
       <c r="C73" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D73" t="n">
-        <v>28.8125</v>
+        <v>35.2432432432432</v>
       </c>
       <c r="E73" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F73" t="n">
-        <v>59.375</v>
+        <v>32.4324324324324</v>
       </c>
     </row>
     <row r="74">
@@ -2162,16 +2162,16 @@
         <v>7</v>
       </c>
       <c r="C74" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D74" t="n">
-        <v>34.3548387096774</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="E74" t="n">
         <v>22</v>
       </c>
       <c r="F74" t="n">
-        <v>29.0322580645161</v>
+        <v>38.8888888888889</v>
       </c>
     </row>
     <row r="75">
@@ -2179,19 +2179,19 @@
         <v>84</v>
       </c>
       <c r="B75" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="C75" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D75" t="n">
-        <v>31.9</v>
+        <v>31.3888888888889</v>
       </c>
       <c r="E75" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F75" t="n">
-        <v>40</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="76">
@@ -2202,16 +2202,16 @@
         <v>7</v>
       </c>
       <c r="C76" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D76" t="n">
-        <v>33.2413793103448</v>
+        <v>30.1666666666667</v>
       </c>
       <c r="E76" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F76" t="n">
-        <v>24.1379310344828</v>
+        <v>47.2222222222222</v>
       </c>
     </row>
     <row r="77">
@@ -2222,16 +2222,16 @@
         <v>7</v>
       </c>
       <c r="C77" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D77" t="n">
-        <v>29.0344827586207</v>
+        <v>34.4285714285714</v>
       </c>
       <c r="E77" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F77" t="n">
-        <v>48.2758620689655</v>
+        <v>28.5714285714286</v>
       </c>
     </row>
     <row r="78">
@@ -2242,16 +2242,16 @@
         <v>7</v>
       </c>
       <c r="C78" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D78" t="n">
-        <v>32.0344827586207</v>
+        <v>29.9411764705882</v>
       </c>
       <c r="E78" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F78" t="n">
-        <v>24.1379310344828</v>
+        <v>44.1176470588235</v>
       </c>
     </row>
     <row r="79">
@@ -2262,16 +2262,16 @@
         <v>7</v>
       </c>
       <c r="C79" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D79" t="n">
-        <v>32.1153846153846</v>
+        <v>33.8125</v>
       </c>
       <c r="E79" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F79" t="n">
-        <v>30.7692307692308</v>
+        <v>34.375</v>
       </c>
     </row>
     <row r="80">
@@ -2282,16 +2282,16 @@
         <v>7</v>
       </c>
       <c r="C80" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D80" t="n">
-        <v>35.6</v>
+        <v>31.3870967741935</v>
       </c>
       <c r="E80" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F80" t="n">
-        <v>40</v>
+        <v>38.7096774193548</v>
       </c>
     </row>
     <row r="81">
@@ -2302,16 +2302,16 @@
         <v>7</v>
       </c>
       <c r="C81" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D81" t="n">
-        <v>25.8333333333333</v>
+        <v>31.7142857142857</v>
       </c>
       <c r="E81" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F81" t="n">
-        <v>58.3333333333333</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82">
@@ -2322,16 +2322,16 @@
         <v>7</v>
       </c>
       <c r="C82" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D82" t="n">
-        <v>28.5652173913043</v>
+        <v>32.72</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F82" t="n">
-        <v>56.5217391304348</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83">
@@ -2342,16 +2342,16 @@
         <v>7</v>
       </c>
       <c r="C83" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D83" t="n">
-        <v>23.3809523809524</v>
+        <v>23.04</v>
       </c>
       <c r="E83" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F83" t="n">
-        <v>71.4285714285714</v>
+        <v>68</v>
       </c>
     </row>
     <row r="84">
@@ -2362,16 +2362,16 @@
         <v>7</v>
       </c>
       <c r="C84" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D84" t="n">
-        <v>31.6190476190476</v>
+        <v>24</v>
       </c>
       <c r="E84" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F84" t="n">
-        <v>19.047619047619</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="85">
@@ -2382,16 +2382,16 @@
         <v>7</v>
       </c>
       <c r="C85" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D85" t="n">
-        <v>30.2</v>
+        <v>30.8260869565217</v>
       </c>
       <c r="E85" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F85" t="n">
-        <v>35</v>
+        <v>26.0869565217391</v>
       </c>
     </row>
     <row r="86">
@@ -2402,16 +2402,16 @@
         <v>7</v>
       </c>
       <c r="C86" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D86" t="n">
-        <v>30.55</v>
+        <v>30.4090909090909</v>
       </c>
       <c r="E86" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F86" t="n">
-        <v>40</v>
+        <v>13.6363636363636</v>
       </c>
     </row>
     <row r="87">
@@ -2422,16 +2422,16 @@
         <v>7</v>
       </c>
       <c r="C87" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D87" t="n">
-        <v>32.1578947368421</v>
+        <v>29.2380952380952</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F87" t="n">
-        <v>47.3684210526316</v>
+        <v>47.6190476190476</v>
       </c>
     </row>
     <row r="88">
@@ -2442,13 +2442,13 @@
         <v>7</v>
       </c>
       <c r="C88" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D88" t="n">
-        <v>28.6111111111111</v>
+        <v>28.65</v>
       </c>
       <c r="E88" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F88" t="n">
         <v>50</v>
@@ -2462,16 +2462,16 @@
         <v>7</v>
       </c>
       <c r="C89" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D89" t="n">
-        <v>30.9375</v>
+        <v>29.95</v>
       </c>
       <c r="E89" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F89" t="n">
-        <v>43.75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="90">
@@ -2482,16 +2482,16 @@
         <v>7</v>
       </c>
       <c r="C90" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D90" t="n">
-        <v>29.8571428571429</v>
+        <v>31.7</v>
       </c>
       <c r="E90" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F90" t="n">
-        <v>42.8571428571429</v>
+        <v>40</v>
       </c>
     </row>
     <row r="91">
@@ -2502,16 +2502,16 @@
         <v>7</v>
       </c>
       <c r="C91" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D91" t="n">
-        <v>32.4285714285714</v>
+        <v>27.3157894736842</v>
       </c>
       <c r="E91" t="n">
         <v>9</v>
       </c>
       <c r="F91" t="n">
-        <v>35.7142857142857</v>
+        <v>52.6315789473684</v>
       </c>
     </row>
     <row r="92">
@@ -2522,16 +2522,16 @@
         <v>9</v>
       </c>
       <c r="C92" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D92" t="n">
-        <v>36.7142857142857</v>
+        <v>27.8888888888889</v>
       </c>
       <c r="E92" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
-        <v>14.2857142857143</v>
+        <v>61.1111111111111</v>
       </c>
     </row>
     <row r="93">
@@ -2542,16 +2542,16 @@
         <v>7</v>
       </c>
       <c r="C93" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D93" t="n">
-        <v>30.75</v>
+        <v>30.2352941176471</v>
       </c>
       <c r="E93" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F93" t="n">
-        <v>58.3333333333333</v>
+        <v>41.1764705882353</v>
       </c>
     </row>
     <row r="94">
@@ -2562,16 +2562,16 @@
         <v>7</v>
       </c>
       <c r="C94" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D94" t="n">
-        <v>30.5833333333333</v>
+        <v>28.9333333333333</v>
       </c>
       <c r="E94" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F94" t="n">
-        <v>41.6666666666667</v>
+        <v>40</v>
       </c>
     </row>
     <row r="95">
@@ -2579,19 +2579,19 @@
         <v>104</v>
       </c>
       <c r="B95" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C95" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D95" t="n">
-        <v>30.5454545454545</v>
+        <v>36.3571428571429</v>
       </c>
       <c r="E95" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F95" t="n">
-        <v>45.4545454545455</v>
+        <v>14.2857142857143</v>
       </c>
     </row>
     <row r="96">
@@ -2602,16 +2602,16 @@
         <v>7</v>
       </c>
       <c r="C96" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D96" t="n">
-        <v>29.7</v>
+        <v>28.6923076923077</v>
       </c>
       <c r="E96" t="n">
         <v>7</v>
       </c>
       <c r="F96" t="n">
-        <v>30</v>
+        <v>46.1538461538462</v>
       </c>
     </row>
     <row r="97">
@@ -2619,19 +2619,19 @@
         <v>106</v>
       </c>
       <c r="B97" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C97" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D97" t="n">
-        <v>30.8888888888889</v>
+        <v>29.9230769230769</v>
       </c>
       <c r="E97" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F97" t="n">
-        <v>33.3333333333333</v>
+        <v>38.4615384615385</v>
       </c>
     </row>
     <row r="98">
@@ -2642,16 +2642,16 @@
         <v>7</v>
       </c>
       <c r="C98" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D98" t="n">
-        <v>32</v>
+        <v>29.7692307692308</v>
       </c>
       <c r="E98" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F98" t="n">
-        <v>14.2857142857143</v>
+        <v>38.4615384615385</v>
       </c>
     </row>
     <row r="99">
@@ -2662,16 +2662,16 @@
         <v>7</v>
       </c>
       <c r="C99" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D99" t="n">
-        <v>28.8571428571429</v>
+        <v>28.8181818181818</v>
       </c>
       <c r="E99" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F99" t="n">
-        <v>42.8571428571429</v>
+        <v>36.3636363636364</v>
       </c>
     </row>
     <row r="100">
@@ -2682,16 +2682,16 @@
         <v>7</v>
       </c>
       <c r="C100" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D100" t="n">
-        <v>31.6666666666667</v>
+        <v>30.625</v>
       </c>
       <c r="E100" t="n">
         <v>6</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="101">
@@ -2702,16 +2702,16 @@
         <v>7</v>
       </c>
       <c r="C101" t="n">
+        <v>8</v>
+      </c>
+      <c r="D101" t="n">
+        <v>28.125</v>
+      </c>
+      <c r="E101" t="n">
         <v>5</v>
       </c>
-      <c r="D101" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="E101" t="n">
-        <v>4</v>
-      </c>
       <c r="F101" t="n">
-        <v>20</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="102">
@@ -2722,16 +2722,16 @@
         <v>7</v>
       </c>
       <c r="C102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D102" t="n">
-        <v>28.2</v>
+        <v>31</v>
       </c>
       <c r="E102" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F102" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2742,16 +2742,16 @@
         <v>7</v>
       </c>
       <c r="C103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D103" t="n">
-        <v>27</v>
+        <v>26.6666666666667</v>
       </c>
       <c r="E103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F103" t="n">
-        <v>40</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="104">
@@ -2762,16 +2762,16 @@
         <v>7</v>
       </c>
       <c r="C104" t="n">
+        <v>5</v>
+      </c>
+      <c r="D104" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="E104" t="n">
         <v>4</v>
       </c>
-      <c r="D104" t="n">
-        <v>27.75</v>
-      </c>
-      <c r="E104" t="n">
-        <v>1</v>
-      </c>
       <c r="F104" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105">
@@ -2785,7 +2785,7 @@
         <v>4</v>
       </c>
       <c r="D105" t="n">
-        <v>35.25</v>
+        <v>35</v>
       </c>
       <c r="E105" t="n">
         <v>3</v>
@@ -2802,16 +2802,16 @@
         <v>7</v>
       </c>
       <c r="C106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D106" t="n">
-        <v>31.5</v>
+        <v>28.6666666666667</v>
       </c>
       <c r="E106" t="n">
         <v>2</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="107">
@@ -3088,13 +3088,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33AFFC4F-ADA1-4E7F-B763-523A60733EDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B57DD39-8671-4501-8211-A7A5CCBF7546}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FE93001-7028-4B1A-B426-EED258F4B7DF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5C8BDDD-DC15-434A-9986-CDE7746717FD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D70109CF-5EF4-4461-AB29-A75A2E10B8A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7372E958-A165-4987-9BAC-13544B3BB5AA}"/>
 </file>
--- a/data/WP17/WP17_auswertung_abgeordnete.xlsx
+++ b/data/WP17/WP17_auswertung_abgeordnete.xlsx
@@ -728,10 +728,10 @@
         <v>32.2196382428941</v>
       </c>
       <c r="E2" t="n">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="F2" t="n">
-        <v>29.7157622739018</v>
+        <v>24.5478036175711</v>
       </c>
     </row>
     <row r="3">
@@ -748,10 +748,10 @@
         <v>26.4474474474474</v>
       </c>
       <c r="E3" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="F3" t="n">
-        <v>64.5645645645646</v>
+        <v>59.4594594594595</v>
       </c>
     </row>
     <row r="4">
@@ -768,10 +768,10 @@
         <v>30.6785714285714</v>
       </c>
       <c r="E4" t="n">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="F4" t="n">
-        <v>50.6493506493507</v>
+        <v>44.4805194805195</v>
       </c>
     </row>
     <row r="5">
@@ -788,10 +788,10 @@
         <v>31.1023102310231</v>
       </c>
       <c r="E5" t="n">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="F5" t="n">
-        <v>41.2541254125413</v>
+        <v>32.3432343234323</v>
       </c>
     </row>
     <row r="6">
@@ -808,10 +808,10 @@
         <v>35.8529411764706</v>
       </c>
       <c r="E6" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F6" t="n">
-        <v>24.6323529411765</v>
+        <v>25.3676470588235</v>
       </c>
     </row>
     <row r="7">
@@ -828,10 +828,10 @@
         <v>34.6642066420664</v>
       </c>
       <c r="E7" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F7" t="n">
-        <v>25.0922509225092</v>
+        <v>24.3542435424354</v>
       </c>
     </row>
     <row r="8">
@@ -848,10 +848,10 @@
         <v>32.0373134328358</v>
       </c>
       <c r="E8" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="F8" t="n">
-        <v>34.7014925373134</v>
+        <v>25.3731343283582</v>
       </c>
     </row>
     <row r="9">
@@ -868,10 +868,10 @@
         <v>31.6260162601626</v>
       </c>
       <c r="E9" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="F9" t="n">
-        <v>34.5528455284553</v>
+        <v>30.4878048780488</v>
       </c>
     </row>
     <row r="10">
@@ -888,10 +888,10 @@
         <v>31.6311475409836</v>
       </c>
       <c r="E10" t="n">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="F10" t="n">
-        <v>33.6065573770492</v>
+        <v>27.4590163934426</v>
       </c>
     </row>
     <row r="11">
@@ -908,10 +908,10 @@
         <v>31.8559670781893</v>
       </c>
       <c r="E11" t="n">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="F11" t="n">
-        <v>41.5637860082305</v>
+        <v>27.1604938271605</v>
       </c>
     </row>
     <row r="12">
@@ -928,10 +928,10 @@
         <v>29.7982062780269</v>
       </c>
       <c r="E12" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="F12" t="n">
-        <v>46.6367713004484</v>
+        <v>40.3587443946188</v>
       </c>
     </row>
     <row r="13">
@@ -948,10 +948,10 @@
         <v>32.8603603603604</v>
       </c>
       <c r="E13" t="n">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="F13" t="n">
-        <v>32.4324324324324</v>
+        <v>27.027027027027</v>
       </c>
     </row>
     <row r="14">
@@ -968,10 +968,10 @@
         <v>31.7647058823529</v>
       </c>
       <c r="E14" t="n">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="F14" t="n">
-        <v>35.2941176470588</v>
+        <v>27.4509803921569</v>
       </c>
     </row>
     <row r="15">
@@ -988,10 +988,10 @@
         <v>31.6032608695652</v>
       </c>
       <c r="E15" t="n">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="F15" t="n">
-        <v>39.6739130434783</v>
+        <v>32.6086956521739</v>
       </c>
     </row>
     <row r="16">
@@ -1008,10 +1008,10 @@
         <v>31.3005464480874</v>
       </c>
       <c r="E16" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F16" t="n">
-        <v>36.6120218579235</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="17">
@@ -1028,10 +1028,10 @@
         <v>32.1396648044693</v>
       </c>
       <c r="E17" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F17" t="n">
-        <v>31.8435754189944</v>
+        <v>32.4022346368715</v>
       </c>
     </row>
     <row r="18">
@@ -1048,10 +1048,10 @@
         <v>31.8</v>
       </c>
       <c r="E18" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="F18" t="n">
-        <v>33.7142857142857</v>
+        <v>26.2857142857143</v>
       </c>
     </row>
     <row r="19">
@@ -1068,10 +1068,10 @@
         <v>30.112426035503</v>
       </c>
       <c r="E19" t="n">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="F19" t="n">
-        <v>42.0118343195266</v>
+        <v>27.2189349112426</v>
       </c>
     </row>
     <row r="20">
@@ -1088,10 +1088,10 @@
         <v>32.0952380952381</v>
       </c>
       <c r="E20" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F20" t="n">
-        <v>41.6666666666667</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="21">
@@ -1108,10 +1108,10 @@
         <v>29.6964285714286</v>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F21" t="n">
-        <v>40.4761904761905</v>
+        <v>38.0952380952381</v>
       </c>
     </row>
     <row r="22">
@@ -1128,10 +1128,10 @@
         <v>34.2994011976048</v>
       </c>
       <c r="E22" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F22" t="n">
-        <v>19.7604790419162</v>
+        <v>17.3652694610778</v>
       </c>
     </row>
     <row r="23">
@@ -1148,10 +1148,10 @@
         <v>29.8791946308725</v>
       </c>
       <c r="E23" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="F23" t="n">
-        <v>44.9664429530201</v>
+        <v>37.5838926174497</v>
       </c>
     </row>
     <row r="24">
@@ -1168,10 +1168,10 @@
         <v>31.9208633093525</v>
       </c>
       <c r="E24" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="F24" t="n">
-        <v>31.6546762589928</v>
+        <v>25.8992805755396</v>
       </c>
     </row>
     <row r="25">
@@ -1188,10 +1188,10 @@
         <v>33.6423357664234</v>
       </c>
       <c r="E25" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F25" t="n">
-        <v>34.3065693430657</v>
+        <v>29.9270072992701</v>
       </c>
     </row>
     <row r="26">
@@ -1208,10 +1208,10 @@
         <v>29.2835820895522</v>
       </c>
       <c r="E26" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F26" t="n">
-        <v>41.044776119403</v>
+        <v>38.0597014925373</v>
       </c>
     </row>
     <row r="27">
@@ -1228,10 +1228,10 @@
         <v>31.1119402985075</v>
       </c>
       <c r="E27" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F27" t="n">
-        <v>44.0298507462687</v>
+        <v>36.5671641791045</v>
       </c>
     </row>
     <row r="28">
@@ -1248,10 +1248,10 @@
         <v>31.5572519083969</v>
       </c>
       <c r="E28" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F28" t="n">
-        <v>32.824427480916</v>
+        <v>26.7175572519084</v>
       </c>
     </row>
     <row r="29">
@@ -1268,10 +1268,10 @@
         <v>33.244094488189</v>
       </c>
       <c r="E29" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F29" t="n">
-        <v>27.5590551181102</v>
+        <v>22.8346456692913</v>
       </c>
     </row>
     <row r="30">
@@ -1288,10 +1288,10 @@
         <v>32.1338582677165</v>
       </c>
       <c r="E30" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F30" t="n">
-        <v>40.9448818897638</v>
+        <v>37.7952755905512</v>
       </c>
     </row>
     <row r="31">
@@ -1308,10 +1308,10 @@
         <v>27.9274193548387</v>
       </c>
       <c r="E31" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F31" t="n">
-        <v>50</v>
+        <v>42.741935483871</v>
       </c>
     </row>
     <row r="32">
@@ -1328,10 +1328,10 @@
         <v>29.447619047619</v>
       </c>
       <c r="E32" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="F32" t="n">
-        <v>46.6666666666667</v>
+        <v>32.3809523809524</v>
       </c>
     </row>
     <row r="33">
@@ -1348,10 +1348,10 @@
         <v>35.02</v>
       </c>
       <c r="E33" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F33" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -1368,10 +1368,10 @@
         <v>47.4285714285714</v>
       </c>
       <c r="E34" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F34" t="n">
-        <v>8.16326530612244</v>
+        <v>7.14285714285714</v>
       </c>
     </row>
     <row r="35">
@@ -1388,10 +1388,10 @@
         <v>31.8</v>
       </c>
       <c r="E35" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F35" t="n">
-        <v>31.1111111111111</v>
+        <v>24.4444444444444</v>
       </c>
     </row>
     <row r="36">
@@ -1408,10 +1408,10 @@
         <v>28.5056179775281</v>
       </c>
       <c r="E36" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F36" t="n">
-        <v>52.808988764045</v>
+        <v>41.5730337078652</v>
       </c>
     </row>
     <row r="37">
@@ -1428,10 +1428,10 @@
         <v>34.1264367816092</v>
       </c>
       <c r="E37" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F37" t="n">
-        <v>34.4827586206897</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="38">
@@ -1448,10 +1448,10 @@
         <v>30.9767441860465</v>
       </c>
       <c r="E38" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F38" t="n">
-        <v>43.0232558139535</v>
+        <v>40.6976744186046</v>
       </c>
     </row>
     <row r="39">
@@ -1468,10 +1468,10 @@
         <v>30.2530120481928</v>
       </c>
       <c r="E39" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F39" t="n">
-        <v>40.9638554216867</v>
+        <v>32.5301204819277</v>
       </c>
     </row>
     <row r="40">
@@ -1488,10 +1488,10 @@
         <v>30.6144578313253</v>
       </c>
       <c r="E40" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F40" t="n">
-        <v>40.9638554216867</v>
+        <v>32.5301204819277</v>
       </c>
     </row>
     <row r="41">
@@ -1508,10 +1508,10 @@
         <v>31.2125</v>
       </c>
       <c r="E41" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F41" t="n">
-        <v>37.5</v>
+        <v>28.75</v>
       </c>
     </row>
     <row r="42">
@@ -1528,10 +1528,10 @@
         <v>29.325</v>
       </c>
       <c r="E42" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F42" t="n">
-        <v>41.25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43">
@@ -1548,10 +1548,10 @@
         <v>31.4025974025974</v>
       </c>
       <c r="E43" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F43" t="n">
-        <v>41.5584415584416</v>
+        <v>25.974025974026</v>
       </c>
     </row>
     <row r="44">
@@ -1588,10 +1588,10 @@
         <v>29.6891891891892</v>
       </c>
       <c r="E45" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="F45" t="n">
-        <v>54.054054054054</v>
+        <v>29.7297297297297</v>
       </c>
     </row>
     <row r="46">
@@ -1608,10 +1608,10 @@
         <v>30.7571428571429</v>
       </c>
       <c r="E46" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F46" t="n">
-        <v>35.7142857142857</v>
+        <v>28.5714285714286</v>
       </c>
     </row>
     <row r="47">
@@ -1628,10 +1628,10 @@
         <v>38.3636363636364</v>
       </c>
       <c r="E47" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F47" t="n">
-        <v>16.6666666666667</v>
+        <v>13.6363636363636</v>
       </c>
     </row>
     <row r="48">
@@ -1648,10 +1648,10 @@
         <v>30.1384615384615</v>
       </c>
       <c r="E48" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F48" t="n">
-        <v>41.5384615384615</v>
+        <v>38.4615384615385</v>
       </c>
     </row>
     <row r="49">
@@ -1668,10 +1668,10 @@
         <v>31.2063492063492</v>
       </c>
       <c r="E49" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F49" t="n">
-        <v>47.6190476190476</v>
+        <v>39.6825396825397</v>
       </c>
     </row>
     <row r="50">
@@ -1688,10 +1688,10 @@
         <v>30.3548387096774</v>
       </c>
       <c r="E50" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F50" t="n">
-        <v>45.1612903225806</v>
+        <v>25.8064516129032</v>
       </c>
     </row>
     <row r="51">
@@ -1708,10 +1708,10 @@
         <v>31.5573770491803</v>
       </c>
       <c r="E51" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F51" t="n">
-        <v>39.344262295082</v>
+        <v>27.8688524590164</v>
       </c>
     </row>
     <row r="52">
@@ -1728,10 +1728,10 @@
         <v>29.4833333333333</v>
       </c>
       <c r="E52" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F52" t="n">
-        <v>45</v>
+        <v>41.6666666666667</v>
       </c>
     </row>
     <row r="53">
@@ -1748,10 +1748,10 @@
         <v>30.6166666666667</v>
       </c>
       <c r="E53" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F53" t="n">
-        <v>43.3333333333333</v>
+        <v>28.3333333333333</v>
       </c>
     </row>
     <row r="54">
@@ -1768,10 +1768,10 @@
         <v>30.6333333333333</v>
       </c>
       <c r="E54" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>43.3333333333333</v>
+        <v>18.3333333333333</v>
       </c>
     </row>
     <row r="55">
@@ -1788,10 +1788,10 @@
         <v>31.9824561403509</v>
       </c>
       <c r="E55" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F55" t="n">
-        <v>40.3508771929825</v>
+        <v>26.3157894736842</v>
       </c>
     </row>
     <row r="56">
@@ -1808,10 +1808,10 @@
         <v>28.1428571428571</v>
       </c>
       <c r="E56" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F56" t="n">
-        <v>60.7142857142857</v>
+        <v>51.7857142857143</v>
       </c>
     </row>
     <row r="57">
@@ -1828,10 +1828,10 @@
         <v>30.3518518518519</v>
       </c>
       <c r="E57" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F57" t="n">
-        <v>42.5925925925926</v>
+        <v>35.1851851851852</v>
       </c>
     </row>
     <row r="58">
@@ -1848,10 +1848,10 @@
         <v>31.25</v>
       </c>
       <c r="E58" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F58" t="n">
-        <v>40.3846153846154</v>
+        <v>23.0769230769231</v>
       </c>
     </row>
     <row r="59">
@@ -1888,10 +1888,10 @@
         <v>31.6458333333333</v>
       </c>
       <c r="E60" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F60" t="n">
-        <v>43.75</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="61">
@@ -1928,10 +1928,10 @@
         <v>32.0212765957447</v>
       </c>
       <c r="E62" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F62" t="n">
-        <v>31.9148936170213</v>
+        <v>23.4042553191489</v>
       </c>
     </row>
     <row r="63">
@@ -1948,10 +1948,10 @@
         <v>29.1395348837209</v>
       </c>
       <c r="E63" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F63" t="n">
-        <v>41.8604651162791</v>
+        <v>39.5348837209302</v>
       </c>
     </row>
     <row r="64">
@@ -1968,10 +1968,10 @@
         <v>28.5714285714286</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F64" t="n">
-        <v>45.2380952380952</v>
+        <v>38.0952380952381</v>
       </c>
     </row>
     <row r="65">
@@ -1988,10 +1988,10 @@
         <v>33.5714285714286</v>
       </c>
       <c r="E65" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F65" t="n">
-        <v>38.0952380952381</v>
+        <v>26.1904761904762</v>
       </c>
     </row>
     <row r="66">
@@ -2008,10 +2008,10 @@
         <v>30.6190476190476</v>
       </c>
       <c r="E66" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F66" t="n">
-        <v>38.0952380952381</v>
+        <v>35.7142857142857</v>
       </c>
     </row>
     <row r="67">
@@ -2028,10 +2028,10 @@
         <v>30.2682926829268</v>
       </c>
       <c r="E67" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F67" t="n">
-        <v>43.9024390243902</v>
+        <v>34.1463414634146</v>
       </c>
     </row>
     <row r="68">
@@ -2048,10 +2048,10 @@
         <v>33.8048780487805</v>
       </c>
       <c r="E68" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F68" t="n">
-        <v>34.1463414634146</v>
+        <v>31.7073170731707</v>
       </c>
     </row>
     <row r="69">
@@ -2068,10 +2068,10 @@
         <v>31.9512195121951</v>
       </c>
       <c r="E69" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F69" t="n">
-        <v>21.9512195121951</v>
+        <v>19.5121951219512</v>
       </c>
     </row>
     <row r="70">
@@ -2088,10 +2088,10 @@
         <v>30.4634146341463</v>
       </c>
       <c r="E70" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F70" t="n">
-        <v>43.9024390243902</v>
+        <v>41.4634146341463</v>
       </c>
     </row>
     <row r="71">
@@ -2108,10 +2108,10 @@
         <v>28.5</v>
       </c>
       <c r="E71" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F71" t="n">
-        <v>50</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="72">
@@ -2148,10 +2148,10 @@
         <v>35.2432432432432</v>
       </c>
       <c r="E73" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F73" t="n">
-        <v>32.4324324324324</v>
+        <v>27.027027027027</v>
       </c>
     </row>
     <row r="74">
@@ -2168,10 +2168,10 @@
         <v>33.3333333333333</v>
       </c>
       <c r="E74" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F74" t="n">
-        <v>38.8888888888889</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="75">
@@ -2188,10 +2188,10 @@
         <v>31.3888888888889</v>
       </c>
       <c r="E75" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F75" t="n">
-        <v>33.3333333333333</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76">
@@ -2208,10 +2208,10 @@
         <v>30.1666666666667</v>
       </c>
       <c r="E76" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F76" t="n">
-        <v>47.2222222222222</v>
+        <v>44.4444444444444</v>
       </c>
     </row>
     <row r="77">
@@ -2228,10 +2228,10 @@
         <v>34.4285714285714</v>
       </c>
       <c r="E77" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F77" t="n">
-        <v>28.5714285714286</v>
+        <v>25.7142857142857</v>
       </c>
     </row>
     <row r="78">
@@ -2248,10 +2248,10 @@
         <v>29.9411764705882</v>
       </c>
       <c r="E78" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F78" t="n">
-        <v>44.1176470588235</v>
+        <v>35.2941176470588</v>
       </c>
     </row>
     <row r="79">
@@ -2268,10 +2268,10 @@
         <v>33.8125</v>
       </c>
       <c r="E79" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F79" t="n">
-        <v>34.375</v>
+        <v>28.125</v>
       </c>
     </row>
     <row r="80">
@@ -2288,10 +2288,10 @@
         <v>31.3870967741935</v>
       </c>
       <c r="E80" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F80" t="n">
-        <v>38.7096774193548</v>
+        <v>35.4838709677419</v>
       </c>
     </row>
     <row r="81">
@@ -2328,10 +2328,10 @@
         <v>32.72</v>
       </c>
       <c r="E82" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F82" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83">
@@ -2348,10 +2348,10 @@
         <v>23.04</v>
       </c>
       <c r="E83" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F83" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="84">
@@ -2408,10 +2408,10 @@
         <v>30.4090909090909</v>
       </c>
       <c r="E86" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F86" t="n">
-        <v>13.6363636363636</v>
+        <v>9.09090909090909</v>
       </c>
     </row>
     <row r="87">
@@ -2428,10 +2428,10 @@
         <v>29.2380952380952</v>
       </c>
       <c r="E87" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F87" t="n">
-        <v>47.6190476190476</v>
+        <v>42.8571428571429</v>
       </c>
     </row>
     <row r="88">
@@ -2448,10 +2448,10 @@
         <v>28.65</v>
       </c>
       <c r="E88" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F88" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="89">
@@ -2468,10 +2468,10 @@
         <v>29.95</v>
       </c>
       <c r="E89" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F89" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90">
@@ -2488,10 +2488,10 @@
         <v>31.7</v>
       </c>
       <c r="E90" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F90" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91">
@@ -2508,10 +2508,10 @@
         <v>27.3157894736842</v>
       </c>
       <c r="E91" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>52.6315789473684</v>
+        <v>47.3684210526316</v>
       </c>
     </row>
     <row r="92">
@@ -2528,10 +2528,10 @@
         <v>27.8888888888889</v>
       </c>
       <c r="E92" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F92" t="n">
-        <v>61.1111111111111</v>
+        <v>55.5555555555556</v>
       </c>
     </row>
     <row r="93">
@@ -2568,10 +2568,10 @@
         <v>28.9333333333333</v>
       </c>
       <c r="E94" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F94" t="n">
-        <v>40</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="95">
@@ -2648,10 +2648,10 @@
         <v>29.7692307692308</v>
       </c>
       <c r="E98" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F98" t="n">
-        <v>38.4615384615385</v>
+        <v>30.7692307692308</v>
       </c>
     </row>
     <row r="99">
@@ -2828,10 +2828,10 @@
         <v>28</v>
       </c>
       <c r="E107" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" t="n">
         <v>0</v>
-      </c>
-      <c r="F107" t="n">
-        <v>100</v>
       </c>
     </row>
     <row r="108">
@@ -3088,13 +3088,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B57DD39-8671-4501-8211-A7A5CCBF7546}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA1EEF3D-4209-4728-AD11-99A60A7C0DE3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5C8BDDD-DC15-434A-9986-CDE7746717FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94F9871A-4215-4F0F-B26A-8ECE13AD6C38}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7372E958-A165-4987-9BAC-13544B3BB5AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EFF0E65-A758-4A53-A878-C9CE4C6326CF}"/>
 </file>